--- a/exports/HBE_Cooling_Load_and_Fan_Schedule.xlsx
+++ b/exports/HBE_Cooling_Load_and_Fan_Schedule.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>POWER CONSUMPTION (WATT)</t>
+          <t>POWER CONSUMPTION (kW)</t>
         </is>
       </c>
       <c r="R7" s="9" t="n"/>
@@ -2096,7 +2096,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>EF D-102</t>
+          <t>EF D-101</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -2142,7 +2142,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>EF D-101</t>
+          <t>EF D-102</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
